--- a/Rolling_Plan_FY26_SM.xlsx
+++ b/Rolling_Plan_FY26_SM.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://rpgnet-my.sharepoint.com/personal/sankuria_kecrpg_com/Documents/Desktop/Vinar/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\rolling-plan-optimizer\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="8_{2DD13D32-5780-4926-AD6A-8D6FED4577C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9F6AA598-E790-4218-82ED-024192363C85}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F5B49D67-8370-45C6-B747-C0B0C2C30534}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{665A50A9-5FBD-46CA-A34C-C9E771F875DC}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="JAN" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">JAN!$A$2:$R$200</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">JAN!$A$2:$Q$200</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="0">JAN!#REF!</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">JAN!$2:$2</definedName>
   </definedNames>
